--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97087</v>
+        <v>97094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97094</v>
+        <v>97103</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49805-2019 artfynd.xlsx
+++ b/artfynd/A 49805-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999162</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
